--- a/Fixture_9na.xlsx
+++ b/Fixture_9na.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\CopaApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D068EB20-28A0-4ED2-B29A-845914A2F52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DB6BBD-1913-4ABC-B484-5B4419B395C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="69">
   <si>
     <r>
       <rPr>
@@ -304,13 +304,127 @@
       </rPr>
       <t>Gyt Celeste</t>
     </r>
+  </si>
+  <si>
+    <t>Hs Inicio</t>
+  </si>
+  <si>
+    <t>Hs Fin</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>10:24</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>10:36</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>11:24</t>
+  </si>
+  <si>
+    <t>11:34</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>12:22</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>12:36</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>13:12</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>13:34</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -363,8 +477,27 @@
       <name val="Palatino Linotype"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,8 +509,14 @@
         <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -400,11 +539,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -440,6 +620,27 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -745,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
@@ -753,9 +954,11 @@
     <col min="3" max="3" width="40.88671875" customWidth="1"/>
     <col min="4" max="4" width="40.44140625" customWidth="1"/>
     <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
@@ -771,8 +974,14 @@
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>5</v>
       </c>
@@ -786,8 +995,20 @@
         <v>3</v>
       </c>
       <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J2" s="13">
+        <v>0.4236111111111111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>5</v>
       </c>
@@ -801,8 +1022,20 @@
         <v>5</v>
       </c>
       <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0.43194444444444446</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>5</v>
       </c>
@@ -816,8 +1049,20 @@
         <v>3</v>
       </c>
       <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0.43333333333333302</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0.44027777777777799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -831,8 +1076,20 @@
         <v>7</v>
       </c>
       <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0.44166666666666698</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.44861111111111102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -846,8 +1103,20 @@
         <v>6</v>
       </c>
       <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0.45</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0.45694444444444399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -861,8 +1130,20 @@
         <v>8</v>
       </c>
       <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0.46527777777777801</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -876,8 +1157,20 @@
         <v>9</v>
       </c>
       <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0.46666666666666701</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0.47361111111111098</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -891,8 +1184,20 @@
         <v>8</v>
       </c>
       <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0.48194444444444501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>5</v>
       </c>
@@ -906,8 +1211,20 @@
         <v>2</v>
       </c>
       <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.483333333333333</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0.49027777777777798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>5</v>
       </c>
@@ -921,8 +1238,20 @@
         <v>6</v>
       </c>
       <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0.49166666666666597</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0.49861111111111101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>5</v>
       </c>
@@ -936,8 +1265,20 @@
         <v>3</v>
       </c>
       <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="13">
+        <v>0.50694444444444497</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>5</v>
       </c>
@@ -951,8 +1292,20 @@
         <v>9</v>
       </c>
       <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0.50833333333333297</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0.51527777777777795</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>5</v>
       </c>
@@ -966,8 +1319,20 @@
         <v>9</v>
       </c>
       <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0.51666666666666605</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0.52361111111111103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>5</v>
       </c>
@@ -981,8 +1346,20 @@
         <v>6</v>
       </c>
       <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="J15" s="13">
+        <v>0.531944444444445</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>5</v>
       </c>
@@ -996,8 +1373,20 @@
         <v>9</v>
       </c>
       <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0.53333333333333299</v>
+      </c>
+      <c r="J16" s="13">
+        <v>0.54027777777777797</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>5</v>
       </c>
@@ -1011,8 +1400,20 @@
         <v>6</v>
       </c>
       <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F17" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="J17" s="13">
+        <v>0.54861111111111105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>6</v>
       </c>
@@ -1026,8 +1427,14 @@
         <v>15</v>
       </c>
       <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F18" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>6</v>
       </c>
@@ -1041,8 +1448,14 @@
         <v>17</v>
       </c>
       <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F19" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>6</v>
       </c>
@@ -1056,8 +1469,14 @@
         <v>14</v>
       </c>
       <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F20" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>6</v>
       </c>
@@ -1071,8 +1490,14 @@
         <v>16</v>
       </c>
       <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F21" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>6</v>
       </c>
@@ -1086,8 +1511,14 @@
         <v>18</v>
       </c>
       <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F22" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>6</v>
       </c>
@@ -1101,8 +1532,14 @@
         <v>17</v>
       </c>
       <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F23" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>6</v>
       </c>
@@ -1116,8 +1553,14 @@
         <v>15</v>
       </c>
       <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F24" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>6</v>
       </c>
@@ -1131,8 +1574,14 @@
         <v>18</v>
       </c>
       <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F25" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>6</v>
       </c>
@@ -1146,8 +1595,14 @@
         <v>14</v>
       </c>
       <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F26" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>6</v>
       </c>
@@ -1161,8 +1616,14 @@
         <v>18</v>
       </c>
       <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>6</v>
       </c>
@@ -1176,8 +1637,14 @@
         <v>21</v>
       </c>
       <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>6</v>
       </c>
@@ -1191,8 +1658,14 @@
         <v>15</v>
       </c>
       <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F29" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>6</v>
       </c>
@@ -1206,8 +1679,14 @@
         <v>18</v>
       </c>
       <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F30" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>6</v>
       </c>
@@ -1221,8 +1700,14 @@
         <v>21</v>
       </c>
       <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F31" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>6</v>
       </c>
@@ -1236,8 +1721,14 @@
         <v>20</v>
       </c>
       <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F32" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>6</v>
       </c>
@@ -1251,8 +1742,14 @@
         <v>21</v>
       </c>
       <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F33" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>7</v>
       </c>
@@ -1266,8 +1763,14 @@
         <v>23</v>
       </c>
       <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F34" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>7</v>
       </c>
@@ -1281,8 +1784,14 @@
         <v>25</v>
       </c>
       <c r="E35" s="5"/>
-    </row>
-    <row r="36" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F35" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>7</v>
       </c>
@@ -1296,8 +1805,14 @@
         <v>22</v>
       </c>
       <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F36" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>7</v>
       </c>
@@ -1311,8 +1826,14 @@
         <v>23</v>
       </c>
       <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F37" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>7</v>
       </c>
@@ -1326,8 +1847,14 @@
         <v>26</v>
       </c>
       <c r="E38" s="5"/>
-    </row>
-    <row r="39" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F38" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>7</v>
       </c>
@@ -1341,8 +1868,14 @@
         <v>28</v>
       </c>
       <c r="E39" s="5"/>
-    </row>
-    <row r="40" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F39" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>7</v>
       </c>
@@ -1356,8 +1889,14 @@
         <v>29</v>
       </c>
       <c r="E40" s="5"/>
-    </row>
-    <row r="41" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F40" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>7</v>
       </c>
@@ -1371,8 +1910,14 @@
         <v>26</v>
       </c>
       <c r="E41" s="5"/>
-    </row>
-    <row r="42" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F41" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>7</v>
       </c>
@@ -1386,8 +1931,14 @@
         <v>27</v>
       </c>
       <c r="E42" s="5"/>
-    </row>
-    <row r="43" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F42" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>7</v>
       </c>
@@ -1401,8 +1952,14 @@
         <v>22</v>
       </c>
       <c r="E43" s="5"/>
-    </row>
-    <row r="44" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F43" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>7</v>
       </c>
@@ -1416,8 +1973,14 @@
         <v>29</v>
       </c>
       <c r="E44" s="5"/>
-    </row>
-    <row r="45" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F44" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>7</v>
       </c>
@@ -1431,8 +1994,14 @@
         <v>23</v>
       </c>
       <c r="E45" s="5"/>
-    </row>
-    <row r="46" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F45" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>7</v>
       </c>
@@ -1446,8 +2015,14 @@
         <v>25</v>
       </c>
       <c r="E46" s="5"/>
-    </row>
-    <row r="47" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F46" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>7</v>
       </c>
@@ -1461,8 +2036,14 @@
         <v>27</v>
       </c>
       <c r="E47" s="5"/>
-    </row>
-    <row r="48" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F47" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>7</v>
       </c>
@@ -1476,8 +2057,14 @@
         <v>30</v>
       </c>
       <c r="E48" s="5"/>
-    </row>
-    <row r="49" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F48" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>7</v>
       </c>
@@ -1491,8 +2078,14 @@
         <v>23</v>
       </c>
       <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F49" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>7</v>
       </c>
@@ -1506,8 +2099,14 @@
         <v>28</v>
       </c>
       <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F50" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>7</v>
       </c>
@@ -1521,8 +2120,14 @@
         <v>28</v>
       </c>
       <c r="E51" s="5"/>
-    </row>
-    <row r="52" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F51" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>8</v>
       </c>
@@ -1536,8 +2141,14 @@
         <v>29</v>
       </c>
       <c r="E52" s="5"/>
-    </row>
-    <row r="53" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F52" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>8</v>
       </c>
@@ -1551,8 +2162,14 @@
         <v>30</v>
       </c>
       <c r="E53" s="5"/>
-    </row>
-    <row r="54" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F53" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>8</v>
       </c>
@@ -1566,8 +2183,14 @@
         <v>29</v>
       </c>
       <c r="E54" s="5"/>
-    </row>
-    <row r="55" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F54" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>8</v>
       </c>
@@ -1581,8 +2204,14 @@
         <v>25</v>
       </c>
       <c r="E55" s="5"/>
-    </row>
-    <row r="56" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F55" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>8</v>
       </c>
@@ -1596,8 +2225,14 @@
         <v>29</v>
       </c>
       <c r="E56" s="5"/>
-    </row>
-    <row r="57" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F56" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>8</v>
       </c>
@@ -1611,8 +2246,14 @@
         <v>27</v>
       </c>
       <c r="E57" s="5"/>
-    </row>
-    <row r="58" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F57" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>8</v>
       </c>
@@ -1626,8 +2267,14 @@
         <v>22</v>
       </c>
       <c r="E58" s="5"/>
-    </row>
-    <row r="59" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F58" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>8</v>
       </c>
@@ -1641,8 +2288,14 @@
         <v>25</v>
       </c>
       <c r="E59" s="5"/>
-    </row>
-    <row r="60" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F59" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>8</v>
       </c>
@@ -1656,8 +2309,14 @@
         <v>30</v>
       </c>
       <c r="E60" s="5"/>
-    </row>
-    <row r="61" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F60" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>8</v>
       </c>
@@ -1671,8 +2330,14 @@
         <v>26</v>
       </c>
       <c r="E61" s="5"/>
-    </row>
-    <row r="62" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F61" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>8</v>
       </c>
@@ -1686,8 +2351,14 @@
         <v>30</v>
       </c>
       <c r="E62" s="5"/>
-    </row>
-    <row r="63" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F62" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>8</v>
       </c>
@@ -1701,8 +2372,14 @@
         <v>27</v>
       </c>
       <c r="E63" s="5"/>
-    </row>
-    <row r="64" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F63" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>8</v>
       </c>
@@ -1716,8 +2393,14 @@
         <v>28</v>
       </c>
       <c r="E64" s="5"/>
-    </row>
-    <row r="65" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F64" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>8</v>
       </c>
@@ -1731,8 +2414,14 @@
         <v>22</v>
       </c>
       <c r="E65" s="5"/>
-    </row>
-    <row r="66" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F65" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
         <v>8</v>
       </c>
@@ -1746,8 +2435,14 @@
         <v>25</v>
       </c>
       <c r="E66" s="5"/>
-    </row>
-    <row r="67" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F66" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>8</v>
       </c>
@@ -1761,8 +2456,14 @@
         <v>27</v>
       </c>
       <c r="E67" s="5"/>
-    </row>
-    <row r="68" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F67" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>8</v>
       </c>
@@ -1776,8 +2477,14 @@
         <v>22</v>
       </c>
       <c r="E68" s="5"/>
-    </row>
-    <row r="69" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="F68" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>8</v>
       </c>
@@ -1791,6 +2498,12 @@
         <v>26</v>
       </c>
       <c r="E69" s="5"/>
+      <c r="F69" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
